--- a/BeatnotePostHotCell/Jun19,2026/Fit_ResultJun19.xlsx
+++ b/BeatnotePostHotCell/Jun19,2026/Fit_ResultJun19.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostHotCell\Jun19,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\Jun19,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DB930D-68AA-48FF-9548-8FC371A3077A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DD69C9-757E-41CE-BD75-20CE3C6B6C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
   <sheets>
     <sheet name="894" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>Date</t>
   </si>
@@ -88,18 +88,12 @@
   <si>
     <t>Jun19,2026+2-56-09PM</t>
   </si>
-  <si>
-    <t>Jun19,2026+2-02-41PM</t>
-  </si>
-  <si>
-    <t>Jun19,2026+2-37-00PM</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -471,9 +465,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C5617D-2BBC-4C21-ADC4-3687FEC8C6E3}">
   <dimension ref="A1:V33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -508,7 +502,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -540,7 +534,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -572,7 +566,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -596,7 +590,7 @@
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -620,7 +614,7 @@
       </c>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -644,7 +638,7 @@
       </c>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -655,7 +649,7 @@
       <c r="H7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -666,7 +660,7 @@
       <c r="H8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -677,7 +671,7 @@
       <c r="H9" s="1"/>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -688,7 +682,7 @@
       <c r="H10" s="1"/>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -699,7 +693,7 @@
       <c r="H11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -710,7 +704,7 @@
       <c r="H12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -721,7 +715,7 @@
       <c r="H13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -732,7 +726,7 @@
       <c r="H14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -743,7 +737,7 @@
       <c r="H15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -754,7 +748,7 @@
       <c r="H16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -764,7 +758,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -774,7 +768,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -784,7 +778,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -794,7 +788,7 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -804,7 +798,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -813,7 +807,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -822,7 +816,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -831,7 +825,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -840,7 +834,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -849,7 +843,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -858,7 +852,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -867,7 +861,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -876,7 +870,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -885,7 +879,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -894,7 +888,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -903,7 +897,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -920,9 +914,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011646E0-737D-49FA-A2CA-7848F848076B}">
   <dimension ref="A1:T40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -958,12 +952,12 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="1">
-        <v>0.17086804073973499</v>
+        <v>0.13307975295074501</v>
       </c>
       <c r="C2" s="1">
         <v>1.5266208406873301</v>
@@ -975,13 +969,13 @@
         <v>-1.6549626245490899E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>3.2276933470753</v>
+        <v>3.1664635139120301</v>
       </c>
       <c r="G2" s="1">
-        <v>39.665599100049903</v>
+        <v>39.665599100091903</v>
       </c>
       <c r="H2" s="1">
-        <v>5.7857693443055499E-4</v>
+        <v>5.7857693438353997E-4</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -992,30 +986,30 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="42.75">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1">
-        <v>0.18219526589061799</v>
+        <v>0.13372258287568001</v>
       </c>
       <c r="C3" s="1">
-        <v>1.52643381409727</v>
+        <v>1.52759869265257</v>
       </c>
       <c r="D3" s="1">
-        <v>2.75859438716609E-3</v>
+        <v>2.0359765500301899E-3</v>
       </c>
       <c r="E3" s="1">
-        <v>-2.5915742623259001E-4</v>
+        <v>-1.72283906292379E-4</v>
       </c>
       <c r="F3" s="1">
-        <v>2.97064097632013</v>
+        <v>2.9169079846133399</v>
       </c>
       <c r="G3" s="1">
-        <v>41.654853269963901</v>
+        <v>39.688246063962303</v>
       </c>
       <c r="H3" s="1">
-        <v>1.15715386862485E-3</v>
+        <v>5.7857698146839801E-4</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1027,137 +1021,105 @@
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
     </row>
-    <row r="4" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="42.75">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
-        <v>0.171697248433512</v>
+        <v>0.13573289163324301</v>
       </c>
       <c r="C4" s="1">
-        <v>1.52759869265257</v>
+        <v>1.5272401774234501</v>
       </c>
       <c r="D4" s="1">
-        <v>2.0359765500301899E-3</v>
+        <v>2.2107522685790699E-3</v>
       </c>
       <c r="E4" s="1">
-        <v>-1.72283906292379E-4</v>
+        <v>-2.0639909087115301E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>2.9781124592999002</v>
+        <v>2.9196017622038299</v>
       </c>
       <c r="G4" s="1">
-        <v>39.688631669368199</v>
+        <v>40.1792585824887</v>
       </c>
       <c r="H4" s="1">
-        <v>5.9539279810936097E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.3027238728623701E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="42.75">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>0.17443666559002999</v>
+        <v>0.13770965349766401</v>
       </c>
       <c r="C5" s="1">
-        <v>1.5272401774234501</v>
+        <v>1.5261618980818801</v>
       </c>
       <c r="D5" s="1">
-        <v>2.2107522685790699E-3</v>
+        <v>2.3479175366752599E-3</v>
       </c>
       <c r="E5" s="1">
-        <v>-2.0639909087115301E-4</v>
+        <v>-1.9603358766553299E-4</v>
       </c>
       <c r="F5" s="1">
-        <v>2.9807998996527201</v>
+        <v>2.9135864205975901</v>
       </c>
       <c r="G5" s="1">
-        <v>41.686575720101402</v>
+        <v>41.706175468619598</v>
       </c>
       <c r="H5" s="1">
-        <v>5.7865730626126201E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.7715365341871501E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="42.75">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>0.169927453472863</v>
+        <v>0.137389858296152</v>
       </c>
       <c r="C6" s="1">
-        <v>1.52724943502682</v>
+        <v>1.5276359260771399</v>
       </c>
       <c r="D6" s="1">
-        <v>2.16852562985549E-3</v>
+        <v>1.9018582425665599E-3</v>
       </c>
       <c r="E6" s="1">
-        <v>-1.97555387689838E-4</v>
+        <v>-1.4403941588760801E-4</v>
       </c>
       <c r="F6" s="1">
-        <v>2.9815161481397201</v>
+        <v>2.9259323454866402</v>
       </c>
       <c r="G6" s="1">
-        <v>39.676011603389199</v>
+        <v>41.743404412322</v>
       </c>
       <c r="H6" s="1">
-        <v>5.8712025513358299E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0.17690051952166999</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1.5261618980818801</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2.3479175366752599E-3</v>
-      </c>
-      <c r="E7" s="1">
-        <v>-1.9603358766553299E-4</v>
-      </c>
-      <c r="F7" s="1">
-        <v>2.9747587355034901</v>
-      </c>
-      <c r="G7" s="1">
-        <v>41.703851987191598</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1.0816786879734399E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1">
-        <v>0.17654554655181801</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1.5276359260771399</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1.9018582425665599E-3</v>
-      </c>
-      <c r="E8" s="1">
-        <v>-1.4403941588760801E-4</v>
-      </c>
-      <c r="F8" s="1">
-        <v>2.9871015003818902</v>
-      </c>
-      <c r="G8" s="1">
-        <v>41.7490343869718</v>
-      </c>
-      <c r="H8" s="1">
-        <v>1.0499748428239499E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+        <v>5.7954114581065602E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1167,7 +1129,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1177,7 +1139,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1187,7 +1149,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1197,7 +1159,7 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1207,7 +1169,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1217,7 +1179,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1227,7 +1189,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1237,7 +1199,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1247,7 +1209,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1257,7 +1219,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1267,7 +1229,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1277,7 +1239,7 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1287,7 +1249,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1297,7 +1259,7 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1307,7 +1269,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1317,7 +1279,7 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1327,7 +1289,7 @@
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1337,7 +1299,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1347,7 +1309,7 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1357,7 +1319,7 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1367,7 +1329,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1377,7 +1339,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1387,7 +1349,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1397,7 +1359,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1407,7 +1369,7 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1417,7 +1379,7 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1427,7 +1389,7 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1437,7 +1399,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1447,7 +1409,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1457,7 +1419,7 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1467,7 +1429,7 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1484,14 +1446,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8CB368-1F4F-4C65-B86B-93EC676CB77B}">
-  <dimension ref="A1:G38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I38"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="11.6328125" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" customWidth="1"/>
+    <col min="1" max="2" width="11.625" customWidth="1"/>
+    <col min="5" max="5" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1502,7 +1464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="28.5">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1510,7 +1472,7 @@
         <v>10.6539096425895</v>
       </c>
       <c r="C2" s="1">
-        <v>0.17086804073973499</v>
+        <v>0.13307975295074501</v>
       </c>
       <c r="F2">
         <v>894</v>
@@ -1518,8 +1480,9 @@
       <c r="G2">
         <v>456</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="28.5">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1527,7 +1490,7 @@
         <v>10.8579810008815</v>
       </c>
       <c r="C3" s="1">
-        <v>0.171697248433512</v>
+        <v>0.13372258287568001</v>
       </c>
       <c r="E3" t="s">
         <v>1</v>
@@ -1538,10 +1501,11 @@
       </c>
       <c r="G3">
         <f>AVERAGE(C2:C33)</f>
-        <v>0.174089604167353</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>0.1355269478506968</v>
+      </c>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="28.5">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -1549,7 +1513,7 @@
         <v>10.831312443746899</v>
       </c>
       <c r="C4" s="1">
-        <v>0.17443666559002999</v>
+        <v>0.13573289163324301</v>
       </c>
       <c r="E4" t="s">
         <v>2</v>
@@ -1560,10 +1524,11 @@
       </c>
       <c r="G4">
         <f>_xlfn.STDEV.S(C2:C33)</f>
-        <v>2.7456869191272077E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>2.0929374066175196E-3</v>
+      </c>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" ht="28.5">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1571,7 +1536,7 @@
         <v>10.709515833036701</v>
       </c>
       <c r="C5" s="1">
-        <v>0.17690051952166999</v>
+        <v>0.13770965349766401</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
@@ -1582,10 +1547,11 @@
       </c>
       <c r="G5">
         <f>G4/G3/SQRT(COUNT(C2:C33))</f>
-        <v>7.0533132928470993E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>6.906302234452379E-3</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" ht="28.5">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1593,157 +1559,158 @@
         <v>10.5903781690852</v>
       </c>
       <c r="C6" s="1">
-        <v>0.17654554655181801</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.137389858296152</v>
+      </c>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3">
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3">
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3">
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3">
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3">
       <c r="C38" s="1"/>
     </row>
   </sheetData>
